--- a/46648_Cuenca_Inambari/_raw_reportes_xlsx/IDConfig_65088_completo.xlsx
+++ b/46648_Cuenca_Inambari/_raw_reportes_xlsx/IDConfig_65088_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R3f051ae05b7f4f23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rab6cf2527cd247df"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,516 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    743.6743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    765.4277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.4707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    765.4277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.4707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.4707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    882.0119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1012.4765</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1068.8191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1127.6573</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1220.7757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1068.8191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1698.5396</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2425.7147</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1698.5396</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1127.6573</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1012.4765</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1319.9836</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1616.5965</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1537.8646</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1354.4571</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    882.0119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    661.5756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    765.4277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.3739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.3739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    503.3147</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -1340,6 +1850,36 @@
       </x:c>
       <x:c s="7" t="inlineStr">
         <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
           <x:t>10:00</x:t>
         </x:is>
       </x:c>
@@ -2860,6 +3400,21 @@
       </x:c>
       <x:c s="3">
         <x:v>    487.8048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/07/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    443.5670</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/46648_Cuenca_Inambari/_raw_reportes_xlsx/IDConfig_65088_completo.xlsx
+++ b/46648_Cuenca_Inambari/_raw_reportes_xlsx/IDConfig_65088_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rab6cf2527cd247df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R57abdb4570ab4c0d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,11 +255,2861 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    586.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    857.6224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    857.6224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    765.4277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    857.6224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    586.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    623.3553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    623.3553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    661.5756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    642.2367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    586.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    623.3553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    661.5756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    661.5756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    765.4277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.4707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    623.3553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    642.2367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    642.2367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    701.6593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    701.6593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    701.6593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    743.6743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.4707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    857.6224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1189.0740</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1220.7757</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1389.6514</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1698.5396</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    552.2409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    552.2409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.3739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    552.2409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    535.5252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    552.2409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    586.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.3739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    586.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    623.3553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    642.2367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.3739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.3739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.3739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    586.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    642.2367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    661.5756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    661.5756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    661.5756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    787.6902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.4707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    906.9565</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    958.5487</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1068.8191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1389.6514</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2370.5589</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    985.2158</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    503.3147</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    503.3147</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    535.5252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    552.2409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    535.5252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    552.2409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    586.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    586.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    623.3553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    623.3553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    642.2367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    701.6593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    765.4277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    623.3553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    701.6593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    701.6593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    623.3553</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    661.5756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    765.4277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    765.4277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    701.6593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    701.6593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    642.2367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    642.2367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    743.6743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    906.9565</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1319.9836</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2012.0641</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.4707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    701.6593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    661.5756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    765.4277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    787.6902</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    857.6224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    882.0119</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1012.4765</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1068.8191</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    765.4277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    857.6224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    519.2190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    519.2190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    535.5252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    552.2409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    552.2409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.3739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    661.5756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    701.6593</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    722.4210</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    765.4277</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.4707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.4707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    857.6224</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    958.5487</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    958.5487</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2370.5589</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   2923.9325</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1189.0740</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    810.4707</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    906.9565</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1012.4765</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1189.0740</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1012.4765</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1127.6573</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>   1253.1540</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    519.2190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    472.6817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    487.8048</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    503.3147</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    503.3147</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    503.3147</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    519.2190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    535.5252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    552.2409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    519.2190</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    535.5252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.3739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.3739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.3739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    569.3739</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    586.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    604.9231</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    642.2367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    642.2367</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
       <x:c s="7" t="inlineStr">
         <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    661.5756</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    681.3803</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
           <x:t>10:00</x:t>
         </x:is>
       </x:c>
@@ -765,6 +3615,66 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    472.6817</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    503.3147</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    535.5252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    552.2409</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -1194,7 +4104,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>    552.2409</x:v>
+        <x:v>    519.2190</x:v>
       </x:c>
     </x:row>
     <x:row>
